--- a/Dhulfiqar_Scouts_Leader_Logins.xlsx
+++ b/Dhulfiqar_Scouts_Leader_Logins.xlsx
@@ -4,24 +4,30 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Leader &amp; Assistant Logins" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Leader &amp; Ṭalīʿah Logins" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="118">
-  <si>
-    <t>⚜️ Dhulfiqār Scouts — Leader &amp; Assistant Login Credentials</t>
-  </si>
-  <si>
-    <t>Portal URL: http://localhost:5173 | Default Password for All Accounts: scouts2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="144">
+  <si>
+    <t>⚜️ Dhulfiqār Scouts — Leader &amp; Ṭalīʿah (Group) Login Credentials</t>
+  </si>
+  <si>
+    <t>Universal Mobile App: http://localhost:5173 | Default Password for All Accounts: scouts2026</t>
   </si>
   <si>
     <t>Grade / Patrol Unit</t>
   </si>
   <si>
+    <t>Ṭalīʿah Rank</t>
+  </si>
+  <si>
+    <t>Ṭalīʿah Group Name</t>
+  </si>
+  <si>
     <t>Role</t>
   </si>
   <si>
@@ -46,6 +52,12 @@
     <t>All Units (Admin)</t>
   </si>
   <si>
+    <t>Troop Command</t>
+  </si>
+  <si>
+    <t>All Troop Units (11 Ṭalāʾiʿ)</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
@@ -61,7 +73,7 @@
     <t>leader@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>Full admin access to all grades &amp; sessions</t>
+    <t>Full admin access to all grades, ṭalāʾiʿ &amp; sessions</t>
   </si>
   <si>
     <t>Troop Admin</t>
@@ -76,6 +88,12 @@
     <t>Kindergarten</t>
   </si>
   <si>
+    <t>Lions - KG</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Mahdi (ʿaj)</t>
+  </si>
+  <si>
     <t>Leader</t>
   </si>
   <si>
@@ -94,6 +112,12 @@
     <t>1st Grade</t>
   </si>
   <si>
+    <t>Tigers - 1st</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Muṣṭafā (ṣ)</t>
+  </si>
+  <si>
     <t>Nader Chamseddine</t>
   </si>
   <si>
@@ -124,6 +148,12 @@
     <t>2nd Grade</t>
   </si>
   <si>
+    <t>Wolf - 2nd</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat aṣ-Ṣādiq (ʿa)</t>
+  </si>
+  <si>
     <t>Jawad Hazime</t>
   </si>
   <si>
@@ -151,6 +181,12 @@
     <t>3rd Grade</t>
   </si>
   <si>
+    <t>Bear - 3rd</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat ar-Riḍā (ʿa)</t>
+  </si>
+  <si>
     <t>Hussein Yahfoufi</t>
   </si>
   <si>
@@ -178,6 +214,12 @@
     <t>4th Grade</t>
   </si>
   <si>
+    <t>Webelos - 4th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat TBD</t>
+  </si>
+  <si>
     <t>Ayman Ayash</t>
   </si>
   <si>
@@ -187,7 +229,7 @@
     <t>aayash@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>4th Grade patrol leader</t>
+    <t>4th Grade patrol leader (Name customizable in portal)</t>
   </si>
   <si>
     <t>Mahdi Hammoud</t>
@@ -214,6 +256,12 @@
     <t>5th Grade</t>
   </si>
   <si>
+    <t>Arrow of Light - 5th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Amīr al-Muʾminīn (ʿa)</t>
+  </si>
+  <si>
     <t>Tamer Safwan</t>
   </si>
   <si>
@@ -250,6 +298,12 @@
     <t>6th Grade</t>
   </si>
   <si>
+    <t>Patrol 1 - 6th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat ʿIshāq al-Ḥusayn (ʿa)</t>
+  </si>
+  <si>
     <t>Mohamad Jalloul</t>
   </si>
   <si>
@@ -277,6 +331,12 @@
     <t>7th Grade</t>
   </si>
   <si>
+    <t>Patrol 2 - 6th/7th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Abū al-Faḍl al-ʿAbbās</t>
+  </si>
+  <si>
     <t>Hassan Issa</t>
   </si>
   <si>
@@ -304,6 +364,12 @@
     <t>8th Grade</t>
   </si>
   <si>
+    <t>Patrol 3 - 8th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Bāqir (ʿa)</t>
+  </si>
+  <si>
     <t>Hasan Yahfoufi</t>
   </si>
   <si>
@@ -331,6 +397,12 @@
     <t>9th Grade</t>
   </si>
   <si>
+    <t>Patrol 4 - 9th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Asadullāh (ʿa)</t>
+  </si>
+  <si>
     <t>Mustapha Mourtada</t>
   </si>
   <si>
@@ -344,6 +416,12 @@
   </si>
   <si>
     <t>10th / 11th Grade</t>
+  </si>
+  <si>
+    <t>Patrol 5 - 10th/11th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Abā ʿAbdillāh (ʿa)</t>
   </si>
   <si>
     <t>Mustapha Choucair</t>
@@ -387,7 +465,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF123C2D"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -398,13 +476,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF0F172A"/>
+      <color rgb="FF17201C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF1D4ED8"/>
+      <color rgb="FF123C2D"/>
       <sz val="10.5"/>
       <name val="Consolas"/>
     </font>
@@ -424,17 +502,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A8A"/>
+        <fgColor rgb="FF123C2D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
+        <fgColor rgb="FFF7F2E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
+        <fgColor rgb="FFB99645"/>
       </patternFill>
     </fill>
     <fill>
@@ -444,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="FFFDFBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -467,7 +545,7 @@
         <color rgb="FF94A3B8"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF1E3A8A"/>
+        <color rgb="FF123C2D"/>
       </bottom>
       <diagonal/>
     </border>
@@ -864,19 +942,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,8 +966,10 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -899,8 +980,10 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -925,635 +1008,785 @@
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7">
+        <v>124</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="11">
+        <v>124</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="11">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="7">
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="11">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="J9" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="7">
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="11">
+        <v>10</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="7">
+        <v>10</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="11">
+        <v>15</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="7">
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="11">
+        <v>15</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="7">
+        <v>14</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="11">
+        <v>14</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="7">
+        <v>14</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" s="11">
+        <v>12</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="7">
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="11">
+        <v>13</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="7">
+        <v>13</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="11">
+        <v>8</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="7">
+        <v>8</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="11">
+        <v>9</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I26" s="7">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7">
-        <v>124</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="J26" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="11">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="11">
-        <v>124</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="7">
-        <v>12</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="11">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="7">
-        <v>11</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="11">
-        <v>10</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="7">
-        <v>10</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="11">
-        <v>10</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="7">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="11">
-        <v>15</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="7">
-        <v>15</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="11">
-        <v>15</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="7">
-        <v>14</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="11">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="7">
-        <v>14</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="11">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="7">
-        <v>12</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="11">
-        <v>13</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="7">
-        <v>13</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="11">
-        <v>8</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="7">
-        <v>8</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="11">
-        <v>9</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="7">
-        <v>11</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" s="11">
-        <v>11</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>114</v>
+      <c r="J27" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
